--- a/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_250923/NA_check_class_and_satisfaction_Session_250923.xlsx
+++ b/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_250923/NA_check_class_and_satisfaction_Session_250923.xlsx
@@ -388,22 +388,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="F2">
-        <v>127</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
